--- a/Progress Reports/CS2 Project Porgress Report Week 1-3.xlsx
+++ b/Progress Reports/CS2 Project Porgress Report Week 1-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elias P Nacaytuna\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AABDBC-2807-4C43-BDA6-92BC745F7ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F59117-A3D2-4BF0-A8AA-2AA3A619E823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="6480" windowWidth="20448" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="week1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     <t>Finished our pseudocode</t>
   </si>
   <si>
-    <t>Week 1 to 3 - Jan 16, 2026  (covers week 1-3 of proj sched)</t>
+    <t>Week 1 - Jan 16, 2026  (covers week 1-3 of proj sched)</t>
   </si>
 </sst>
 </file>
